--- a/FOYER-ZERO-CALIBRAGE-2.xlsx
+++ b/FOYER-ZERO-CALIBRAGE-2.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96750C4B-E342-1743-93AB-56C04061B8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E76FF97C-F82B-0048-B7DE-DB9ADEF8DF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LISEZ-MOI" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="271">
   <si>
     <t>Foyer Zéro — classeur de calibrage</t>
   </si>
@@ -835,9 +835,6 @@
   </si>
   <si>
     <t xml:space="preserve">base sera toujours +10% rempli par rapport à l'avant poste du même niveau </t>
-  </si>
-  <si>
-    <t xml:space="preserve">j'ai pas compris j'ai mis au pif </t>
   </si>
   <si>
     <t>message d'Ethan pour claude</t>
@@ -1492,22 +1489,22 @@
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B33" s="28" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B35" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -4216,7 +4213,7 @@
         <v>153</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>154</v>
@@ -4444,10 +4441,10 @@
         <v>105</v>
       </c>
       <c r="B11" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>264</v>
       </c>
       <c r="D11" s="14">
         <v>1</v>
@@ -4518,28 +4515,28 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>266</v>
+      </c>
+      <c r="B17" t="s">
         <v>267</v>
-      </c>
-      <c r="B17" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>268</v>
+      </c>
+      <c r="B18" t="s">
         <v>269</v>
-      </c>
-      <c r="B18" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -4554,7 +4551,7 @@
   <sheetFormatPr defaultColWidth="8.7421875" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.01171875" customWidth="1"/>
-    <col min="2" max="2" width="13.98828125" customWidth="1"/>
+    <col min="2" max="2" width="10.76171875" customWidth="1"/>
     <col min="3" max="3" width="13.046875" customWidth="1"/>
     <col min="4" max="4" width="11.97265625" customWidth="1"/>
     <col min="5" max="6" width="9.01171875" customWidth="1"/>
@@ -4630,9 +4627,9 @@
         <f>(F5/6)*100</f>
         <v>1.8518518518518516</v>
       </c>
-      <c r="H5" s="27">
-        <f>(G5/6)*100</f>
-        <v>30.864197530864196</v>
+      <c r="H5" s="29">
+        <f>G5/10</f>
+        <v>0.18518518518518517</v>
       </c>
       <c r="I5" s="14" t="s">
         <v>255</v>
@@ -4666,9 +4663,9 @@
         <f>(F6/6)*100</f>
         <v>2.3148148148148149</v>
       </c>
-      <c r="H6" s="27">
-        <f>(G6/6)*100</f>
-        <v>38.580246913580247</v>
+      <c r="H6" s="29">
+        <f t="shared" ref="H6:H24" si="0">G6/10</f>
+        <v>0.23148148148148148</v>
       </c>
       <c r="I6" s="14"/>
       <c r="J6" s="14"/>
@@ -4698,9 +4695,9 @@
         <f>(F7/6)*100</f>
         <v>2.5462962962962967</v>
       </c>
-      <c r="H7" s="27">
-        <f>(G7/6)*100</f>
-        <v>42.438271604938279</v>
+      <c r="H7" s="29">
+        <f t="shared" si="0"/>
+        <v>0.25462962962962965</v>
       </c>
       <c r="I7" s="14"/>
       <c r="J7" s="14"/>
@@ -4730,9 +4727,9 @@
         <f>(F8/6)*100</f>
         <v>3.0092592592592591</v>
       </c>
-      <c r="H8" s="27">
-        <f>(G8/6)*100</f>
-        <v>50.154320987654323</v>
+      <c r="H8" s="29">
+        <f t="shared" si="0"/>
+        <v>0.30092592592592593</v>
       </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
@@ -4762,9 +4759,9 @@
         <f>(F9/6)*100</f>
         <v>3.2407407407407405</v>
       </c>
-      <c r="H9" s="27">
-        <f>(G9/6)*100</f>
-        <v>54.012345679012341</v>
+      <c r="H9" s="29">
+        <f t="shared" si="0"/>
+        <v>0.32407407407407407</v>
       </c>
       <c r="I9" s="14"/>
       <c r="J9" s="14"/>
@@ -4794,9 +4791,9 @@
         <f>(F10/6)*100</f>
         <v>4.3981481481481479</v>
       </c>
-      <c r="H10" s="27">
-        <f>(G10/6)*100</f>
-        <v>73.302469135802468</v>
+      <c r="H10" s="29">
+        <f t="shared" si="0"/>
+        <v>0.43981481481481477</v>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14"/>
@@ -4826,9 +4823,9 @@
         <f>(F11/6)*100</f>
         <v>3.7037037037037033</v>
       </c>
-      <c r="H11" s="27">
-        <f>(G11/6)*100</f>
-        <v>61.728395061728392</v>
+      <c r="H11" s="29">
+        <f t="shared" si="0"/>
+        <v>0.37037037037037035</v>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14"/>
@@ -4858,9 +4855,9 @@
         <f>(F12/6)*100</f>
         <v>5.5555555555555554</v>
       </c>
-      <c r="H12" s="27">
-        <f>(G12/6)*100</f>
-        <v>92.592592592592595</v>
+      <c r="H12" s="29">
+        <f t="shared" si="0"/>
+        <v>0.55555555555555558</v>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14"/>
@@ -4890,9 +4887,9 @@
         <f>(F13/6)*100</f>
         <v>4.1666666666666661</v>
       </c>
-      <c r="H13" s="27">
-        <f>(G13/6)*100</f>
-        <v>69.444444444444429</v>
+      <c r="H13" s="29">
+        <f t="shared" si="0"/>
+        <v>0.41666666666666663</v>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14"/>
@@ -4922,9 +4919,9 @@
         <f>(F14/6)*100</f>
         <v>6.481481481481481</v>
       </c>
-      <c r="H14" s="27">
-        <f>(G14/6)*100</f>
-        <v>108.02469135802468</v>
+      <c r="H14" s="29">
+        <f t="shared" si="0"/>
+        <v>0.64814814814814814</v>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14"/>
@@ -4954,9 +4951,9 @@
         <f>(F15/6)*100</f>
         <v>4.8611111111111116</v>
       </c>
-      <c r="H15" s="27">
-        <f>(G15/6)*100</f>
-        <v>81.018518518518519</v>
+      <c r="H15" s="29">
+        <f t="shared" si="0"/>
+        <v>0.48611111111111116</v>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14"/>
@@ -4986,9 +4983,9 @@
         <f>(F16/6)*100</f>
         <v>7.1759259259259256</v>
       </c>
-      <c r="H16" s="27">
-        <f>(G16/6)*100</f>
-        <v>119.59876543209876</v>
+      <c r="H16" s="29">
+        <f t="shared" si="0"/>
+        <v>0.71759259259259256</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14"/>
@@ -5018,9 +5015,9 @@
         <f>(F17/6)*100</f>
         <v>5.3240740740740735</v>
       </c>
-      <c r="H17" s="27">
-        <f>(G17/6)*100</f>
-        <v>88.734567901234556</v>
+      <c r="H17" s="29">
+        <f t="shared" si="0"/>
+        <v>0.53240740740740733</v>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14"/>
@@ -5050,9 +5047,9 @@
         <f>(F18/6)*100</f>
         <v>7.6388888888888884</v>
       </c>
-      <c r="H18" s="27">
-        <f>(G18/6)*100</f>
-        <v>127.31481481481481</v>
+      <c r="H18" s="29">
+        <f t="shared" si="0"/>
+        <v>0.76388888888888884</v>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14"/>
@@ -5082,9 +5079,9 @@
         <f>(F19/6)*100</f>
         <v>5.7870370370370372</v>
       </c>
-      <c r="H19" s="27">
-        <f>(G19/6)*100</f>
-        <v>96.450617283950621</v>
+      <c r="H19" s="29">
+        <f t="shared" si="0"/>
+        <v>0.57870370370370372</v>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14"/>
@@ -5114,9 +5111,9 @@
         <f>(F20/6)*100</f>
         <v>8.1018518518518512</v>
       </c>
-      <c r="H20" s="27">
-        <f>(G20/6)*100</f>
-        <v>135.03086419753086</v>
+      <c r="H20" s="29">
+        <f t="shared" si="0"/>
+        <v>0.81018518518518512</v>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14"/>
@@ -5146,9 +5143,9 @@
         <f>(F21/6)*100</f>
         <v>5.7870370370370372</v>
       </c>
-      <c r="H21" s="27">
-        <f>(G21/6)*100</f>
-        <v>96.450617283950621</v>
+      <c r="H21" s="29">
+        <f t="shared" si="0"/>
+        <v>0.57870370370370372</v>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14"/>
@@ -5178,9 +5175,9 @@
         <f>(F22/6)*100</f>
         <v>8.1018518518518512</v>
       </c>
-      <c r="H22" s="27">
-        <f>(G22/6)*100</f>
-        <v>135.03086419753086</v>
+      <c r="H22" s="29">
+        <f t="shared" si="0"/>
+        <v>0.81018518518518512</v>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14"/>
@@ -5210,9 +5207,9 @@
         <f>(F23/6)*100</f>
         <v>5.7870370370370372</v>
       </c>
-      <c r="H23" s="27">
-        <f>(G23/6)*100</f>
-        <v>96.450617283950621</v>
+      <c r="H23" s="29">
+        <f t="shared" si="0"/>
+        <v>0.57870370370370372</v>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14"/>
@@ -5242,18 +5239,15 @@
         <f>(F24/6)*100</f>
         <v>8.1018518518518512</v>
       </c>
-      <c r="H24" s="27">
-        <f>(G24/6)*100</f>
-        <v>135.03086419753086</v>
+      <c r="H24" s="29">
+        <f t="shared" si="0"/>
+        <v>0.81018518518518512</v>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="F25" s="26"/>
-      <c r="H25" t="s">
-        <v>258</v>
-      </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">

--- a/FOYER-ZERO-CALIBRAGE-2.xlsx
+++ b/FOYER-ZERO-CALIBRAGE-2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E76FF97C-F82B-0048-B7DE-DB9ADEF8DF26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63322430-8F4D-D741-B46D-3B545426E375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
